--- a/ru/downloads/data-excel/11.5.1.xlsx
+++ b/ru/downloads/data-excel/11.5.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10635"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="49">
   <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
@@ -287,7 +287,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -385,6 +385,15 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -669,14 +678,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T35"/>
+  <dimension ref="A1:U35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="32.7109375" customWidth="1"/>
     <col min="4" max="20" width="8.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>46</v>
       </c>
@@ -687,7 +696,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>42</v>
       </c>
@@ -698,7 +707,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -719,8 +728,9 @@
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="8"/>
-    </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>0</v>
       </c>
@@ -781,8 +791,11 @@
       <c r="T4" s="12">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U4" s="12">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -843,8 +856,11 @@
       <c r="T5" s="13">
         <v>44</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U5" s="13">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>36</v>
       </c>
@@ -905,8 +921,11 @@
       <c r="T6" s="20">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U6" s="35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>37</v>
       </c>
@@ -967,8 +986,11 @@
       <c r="T7" s="21">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U7" s="35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1051,11 @@
       <c r="T8" s="31" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U8" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
@@ -1091,8 +1116,11 @@
       <c r="T9" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U9" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>37</v>
       </c>
@@ -1153,8 +1181,11 @@
       <c r="T10" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U10" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1215,8 +1246,11 @@
       <c r="T11" s="34">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U11" s="13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>36</v>
       </c>
@@ -1277,8 +1311,11 @@
       <c r="T12" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U12" s="35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>37</v>
       </c>
@@ -1339,8 +1376,11 @@
       <c r="T13" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U13" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1401,8 +1441,11 @@
       <c r="T14" s="34">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U14" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>36</v>
       </c>
@@ -1463,8 +1506,11 @@
       <c r="T15" s="20">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U15" s="35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>37</v>
       </c>
@@ -1525,8 +1571,11 @@
       <c r="T16" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U16" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
@@ -1587,8 +1636,11 @@
       <c r="T17" s="34">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U17" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>36</v>
       </c>
@@ -1649,8 +1701,11 @@
       <c r="T18" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>37</v>
       </c>
@@ -1711,8 +1766,11 @@
       <c r="T19" s="21">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U19" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
@@ -1773,8 +1831,11 @@
       <c r="T20" s="34">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U20" s="13">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>36</v>
       </c>
@@ -1835,8 +1896,11 @@
       <c r="T21" s="20">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U21" s="35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>37</v>
       </c>
@@ -1897,8 +1961,11 @@
       <c r="T22" s="21">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U22" s="35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
@@ -1959,8 +2026,11 @@
       <c r="T23" s="34" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U23" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>36</v>
       </c>
@@ -2021,8 +2091,11 @@
       <c r="T24" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U24" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>37</v>
       </c>
@@ -2083,8 +2156,11 @@
       <c r="T25" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U25" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
@@ -2145,8 +2221,11 @@
       <c r="T26" s="34">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U26" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>36</v>
       </c>
@@ -2207,8 +2286,11 @@
       <c r="T27" s="20">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U27" s="35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>37</v>
       </c>
@@ -2269,8 +2351,11 @@
       <c r="T28" s="21">
         <v>8</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U28" s="35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" s="32" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
         <v>27</v>
       </c>
@@ -2331,8 +2416,11 @@
       <c r="T29" s="34" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U29" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>36</v>
       </c>
@@ -2393,8 +2481,11 @@
       <c r="T30" s="20" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U30" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>37</v>
       </c>
@@ -2455,8 +2546,11 @@
       <c r="T31" s="21" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="U31" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
         <v>30</v>
       </c>
@@ -2517,8 +2611,11 @@
       <c r="T32" s="31">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U32" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>36</v>
       </c>
@@ -2579,8 +2676,11 @@
       <c r="T33" s="20">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U33" s="35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>37</v>
       </c>
@@ -2641,8 +2741,11 @@
       <c r="T34" s="24" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U34" s="37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>45</v>
       </c>
